--- a/eventos_mineracao_geotecnia_2026.xlsx
+++ b/eventos_mineracao_geotecnia_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itinfoalvarezandmarsal.sharepoint.com/sites/IniciativasEstratgicasMinerao/Propostas/19. Gerdau_Projeto Gerência de Geotecnia/05. Implantação de PMO (continuidade 2026)/07. PMO Performance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itinfoalvarezandmarsalbra.sharepoint.com/sites/GERDAUImplantaodePMO/Shared Documents/Reports GERDAU/PMO de Performance/Report_GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{AFBFD803-061B-4256-A828-CFB558E1B3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B08CF19E-2A72-47DE-8936-F8220061440F}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{AFBFD803-061B-4256-A828-CFB558E1B3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{983E2B39-7432-4E91-9061-CD5074D3A563}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="1272" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eventos 2026" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="112">
   <si>
     <t>CALENDÁRIO DE EVENTOS DE MINERAÇÃO E GEOTECNIA - BRASIL 2026</t>
   </si>
@@ -394,6 +394,9 @@
   </si>
   <si>
     <t>Média a alta - relevante para a equipe de barragens</t>
+  </si>
+  <si>
+    <t>Data de atualização</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,6 +504,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -529,7 +538,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -564,6 +573,8 @@
     <xf numFmtId="16" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -894,26 +905,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="2:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="17">
+        <f ca="1">TODAY()</f>
+        <v>46170</v>
+      </c>
     </row>
     <row r="4" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -1207,243 +1227,243 @@
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
     </row>
     <row r="38" spans="2:8" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
     </row>
     <row r="39" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="B4:H16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1484,8 +1504,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B85E9BD78952D949AD3876755849F106" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="30b165b1fc8abf4931cc9e258ef59508">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dbba7408-ec95-4851-bc50-df263b655ec0" xmlns:ns3="e6953d52-380c-40a2-8363-431c2cfb0bc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5918ea9ac9532f027873cd77c25c9478" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B85E9BD78952D949AD3876755849F106" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4aa88d9fe912cafe686c6cbf65837abc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dbba7408-ec95-4851-bc50-df263b655ec0" xmlns:ns3="e6953d52-380c-40a2-8363-431c2cfb0bc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="547b89ab8c350a17ac85302bf0dfa979" ns2:_="" ns3:_="">
     <xsd:import namespace="dbba7408-ec95-4851-bc50-df263b655ec0"/>
     <xsd:import namespace="e6953d52-380c-40a2-8363-431c2cfb0bc0"/>
     <xsd:element name="properties">
@@ -1533,7 +1553,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6830aa7a-1173-4a8f-8fff-517453f03437" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6830aa7a-1173-4a8f-8fff-517453f03437" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1582,8 +1602,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1692,7 +1712,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71B4C5F2-72FB-4B15-B9C7-EBB217664CB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E15CC99-8F3D-494A-8083-0CDC3FD8ACC5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1702,6 +1722,8 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="62085a58-89d2-499f-8d94-3bd68bf2bcd0"/>
     <ds:schemaRef ds:uri="afd69eaf-c895-4734-b5c3-ccfe75373e30"/>
+    <ds:schemaRef ds:uri="e6953d52-380c-40a2-8363-431c2cfb0bc0"/>
+    <ds:schemaRef ds:uri="dbba7408-ec95-4851-bc50-df263b655ec0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>